--- a/gd/excel/item.xlsx
+++ b/gd/excel/item.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -96,11 +96,53 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +160,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +606,7 @@
           <t>drop_range</t>
         </is>
       </c>
-      <c r="G1" s="4" t="n"/>
+      <c r="G1" s="7" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>tags</t>
@@ -575,11 +619,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>min</t>
@@ -590,8 +634,8 @@
           <t>max</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -687,16 +731,330 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>铁剑</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>火焰长剑</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1,5,10</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>传说之剑</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1,5,10,15</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>皮甲</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>80</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>板甲</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2,6,10</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>治疗药水</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>大型治疗药水</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3,7,11</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4001</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>铁矿石</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>魔晶石</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,8,12</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:I1000">

--- a/gd/excel/item.xlsx
+++ b/gd/excel/item.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>精铁剑</t>
         </is>
       </c>
       <c r="C5" t="n">

--- a/gd/excel/item.xlsx
+++ b/gd/excel/item.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,19 +32,13 @@
       <sz val="12"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <i val="1"/>
-      <color rgb="001B4332"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="微软雅黑"/>
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C9A227"/>
         <bgColor rgb="00C9A227"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F3DC"/>
-        <bgColor rgb="00D8F3DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,72 +84,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -561,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,489 +516,308 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">name
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string[i18n]</t>
+          </r>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">price
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>rarity</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">rarity
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>enum[common,rare,epic]</t>
+          </r>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>item_type_id</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">item_type_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32[ref:item_type.id]</t>
+          </r>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>drop_range</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="n"/>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">drop_range
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>DropRange</t>
+          </r>
+        </is>
+      </c>
+      <c r="G1" s="4" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>tags</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">tags
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>array&lt;int32&gt;</t>
+          </r>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">is_active
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>bool</t>
+          </r>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>min</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">min
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">max
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>道具唯一ID，禁止修改</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>string[i18n]</t>
+          <t>道具名称（多语言）</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>售价（金币），0=不可出售</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>enum[common,rare,epic]</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>int32[ref:item_type.id]</t>
+          <t>道具类型，关联 item_type.id</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>掉落数量下限</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>掉落数量上限</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>array&lt;int32&gt;</t>
+          <t>标签列表，逗号分隔</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>是否启用（仅服务端）</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>道具唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>道具名称（多语言）</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>售价（金币），0=不可出售</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>稀有度</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>道具类型，关联 item_type.id</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>掉落数量下限</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>掉落数量上限</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>标签列表，逗号分隔</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>是否启用（仅服务端）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>精铁剑</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>火焰长剑</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1,5,10</t>
-        </is>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>传说之剑</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1,5,10,15</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>皮甲</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>80</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>板甲</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2,6,10</t>
-        </is>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3001</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>治疗药水</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>3002</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>大型治疗药水</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>80</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3,7,11</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4001</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>铁矿石</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>4002</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>魔晶石</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4,8,12</t>
-        </is>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="4"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:I1000">
+  <conditionalFormatting sqref="A4:I1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -1066,7 +826,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"common,rare,epic"</formula1>
     </dataValidation>
   </dataValidations>

--- a/gd/excel/item.xlsx
+++ b/gd/excel/item.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Item" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -70,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -84,11 +84,53 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,6 +145,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -519,244 +563,74 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
-          </r>
+          <t>Id
+int32</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">name
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>string[i18n]</t>
-          </r>
+          <t>Name
+string[i18n]</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">price
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>float</t>
-          </r>
+          <t>Price
+float</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">rarity
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>enum[common,rare,epic]</t>
-          </r>
+          <t>Rarity
+enum[common,rare,epic]</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">item_type_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32[ref:item_type.id]</t>
-          </r>
+          <t>ItemTypeId
+int32[ref:ItemType.Id]</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">drop_range
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>DropRange</t>
-          </r>
-        </is>
-      </c>
-      <c r="G1" s="4" t="n"/>
+          <t>DropRange
+Droprange</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">tags
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>array&lt;int32&gt;</t>
-          </r>
+          <t>Tags
+array&lt;int32&gt;</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">is_active
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>bool</t>
-          </r>
+          <t>IsActive
+bool</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">min
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
-          </r>
+          <t>Min
+int32</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">max
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
-          </r>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
+          <t>Max
+int32</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -781,7 +655,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>道具类型，关联 item_type.id</t>
+          <t>道具类型，关联 ItemType.Id</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -805,16 +679,155 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>药水</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>101,102</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>铁剑</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>魔法石</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>250</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>301,302,303</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>面包</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:I1000">
